--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,14 +851,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45163.60857907718</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -900,24 +896,6 @@
       <c r="A11" s="22" t="n"/>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -949,7 +927,7 @@
       </c>
       <c r="C31" s="25" t="n"/>
       <c r="D31" s="26" t="n">
-        <v>1759.115</v>
+        <v>2022.982</v>
       </c>
       <c r="E31" s="27" t="n"/>
       <c r="F31" s="27" t="n"/>
@@ -967,7 +945,7 @@
       </c>
       <c r="C32" s="25" t="n"/>
       <c r="D32" s="26" t="n">
-        <v>726.827</v>
+        <v>835.851</v>
       </c>
       <c r="E32" s="27" t="n"/>
       <c r="F32" s="27" t="n"/>
@@ -985,7 +963,7 @@
       </c>
       <c r="C33" s="25" t="n"/>
       <c r="D33" s="26" t="n">
-        <v>1491.591</v>
+        <v>1715.33</v>
       </c>
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="27" t="n"/>
@@ -1007,8 +985,6 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" s="1"/>
     <row r="40" ht="15.75" customHeight="1" s="1"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1016,15 +992,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1033,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,7 +851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45237</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
@@ -1000,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,7 +851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
@@ -1000,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -1000,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,7 +851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
@@ -1000,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,7 +851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,10 +851,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45266</v>
+        <v>45261.57770526375</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -896,6 +900,24 @@
       <c r="A11" s="22" t="n"/>
       <c r="E11" s="11" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -927,7 +949,7 @@
       </c>
       <c r="C31" s="25" t="n"/>
       <c r="D31" s="26" t="n">
-        <v>2022.982</v>
+        <v>3096.47</v>
       </c>
       <c r="E31" s="27" t="n"/>
       <c r="F31" s="27" t="n"/>
@@ -945,7 +967,7 @@
       </c>
       <c r="C32" s="25" t="n"/>
       <c r="D32" s="26" t="n">
-        <v>835.851</v>
+        <v>1279.39</v>
       </c>
       <c r="E32" s="27" t="n"/>
       <c r="F32" s="27" t="n"/>
@@ -963,7 +985,7 @@
       </c>
       <c r="C33" s="25" t="n"/>
       <c r="D33" s="26" t="n">
-        <v>1715.33</v>
+        <v>2625.56</v>
       </c>
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="27" t="n"/>
@@ -985,6 +1007,8 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" s="1"/>
     <row r="40" ht="15.75" customHeight="1" s="1"/>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -992,6 +1016,15 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1000,14 +1033,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
+++ b/LISTAS/mi/CERRADURA PARA MUEBLES.xlsx
@@ -851,14 +851,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45261.57770526375</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="23" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -900,24 +896,6 @@
       <c r="A11" s="22" t="n"/>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -949,7 +927,7 @@
       </c>
       <c r="C31" s="25" t="n"/>
       <c r="D31" s="26" t="n">
-        <v>3096.47</v>
+        <v>2022.982</v>
       </c>
       <c r="E31" s="27" t="n"/>
       <c r="F31" s="27" t="n"/>
@@ -967,7 +945,7 @@
       </c>
       <c r="C32" s="25" t="n"/>
       <c r="D32" s="26" t="n">
-        <v>1279.39</v>
+        <v>835.851</v>
       </c>
       <c r="E32" s="27" t="n"/>
       <c r="F32" s="27" t="n"/>
@@ -985,7 +963,7 @@
       </c>
       <c r="C33" s="25" t="n"/>
       <c r="D33" s="26" t="n">
-        <v>2625.56</v>
+        <v>1715.33</v>
       </c>
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="27" t="n"/>
@@ -1007,8 +985,6 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" s="1"/>
     <row r="40" ht="15.75" customHeight="1" s="1"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1016,15 +992,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1033,14 +1000,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
